--- a/data/Capacitacion/procesar/layoutPrueba.xlsx
+++ b/data/Capacitacion/procesar/layoutPrueba.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\SSIS_MX\Agente VAPI\API\Capacitacion\procesar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ikeasistencia0-my.sharepoint.com/personal/abolom_ikeasistencia_com/Documents/Documentos/1.-proyectos_ike/python/1.-Capacitacion_RH/1.-API - copia/data/Capacitacion/procesar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEF93A3-3C59-4329-A916-7D8CDC471E9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{16062AB9-70A9-4208-A972-0065B5D7523B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{235F85BF-B99C-4AC6-9AD9-F0D34EFEFD8E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{580B104C-87EA-4B4E-8DBB-FEEBBC5B377A}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>numero</t>
   </si>
@@ -33,9 +33,6 @@
     <t>nombre</t>
   </si>
   <si>
-    <t xml:space="preserve">alejandro </t>
-  </si>
-  <si>
     <t>clservicio</t>
   </si>
   <si>
@@ -54,16 +51,16 @@
     <t>1</t>
   </si>
   <si>
-    <t>prueba</t>
-  </si>
-  <si>
     <t>extension</t>
   </si>
   <si>
-    <t>+525554800970</t>
-  </si>
-  <si>
-    <t>600543</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>+525539181750</t>
+  </si>
+  <si>
+    <t>377</t>
   </si>
 </sst>
 </file>
@@ -117,6 +114,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -436,13 +437,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A371FA-7A36-4560-8D38-8A7A76AD455A}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" style="1"/>
-    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="1" customWidth="1"/>
     <col min="5" max="5" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.44140625" style="1" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" style="1"/>
@@ -452,55 +453,46 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Capacitacion/procesar/layoutPrueba.xlsx
+++ b/data/Capacitacion/procesar/layoutPrueba.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ikeasistencia0-my.sharepoint.com/personal/abolom_ikeasistencia_com/Documents/Documentos/1.-proyectos_ike/python/1.-Capacitacion_RH/1.-API - copia/data/Capacitacion/procesar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ikeasistencia0-my.sharepoint.com/personal/abolom_ikeasistencia_com/Documents/Documentos/1.-proyectos_ike/python/1.-Capacitacion_RH/2.-API.version_2.25022026/data/Capacitacion/procesar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{16062AB9-70A9-4208-A972-0065B5D7523B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{235F85BF-B99C-4AC6-9AD9-F0D34EFEFD8E}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:1_{16062AB9-70A9-4208-A972-0065B5D7523B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66132BC0-1B5C-412B-B89D-DD597549A028}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{580B104C-87EA-4B4E-8DBB-FEEBBC5B377A}"/>
   </bookViews>
@@ -54,13 +54,13 @@
     <t>extension</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>+525539181750</t>
   </si>
   <si>
-    <t>377</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>399</t>
   </si>
 </sst>
 </file>
@@ -482,10 +482,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>11</v>

--- a/data/Capacitacion/procesar/layoutPrueba.xlsx
+++ b/data/Capacitacion/procesar/layoutPrueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ikeasistencia0-my.sharepoint.com/personal/abolom_ikeasistencia_com/Documents/Documentos/1.-proyectos_ike/python/1.-Capacitacion_RH/2.-API.version_2.25022026/data/Capacitacion/procesar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:1_{16062AB9-70A9-4208-A972-0065B5D7523B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66132BC0-1B5C-412B-B89D-DD597549A028}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="114_{21CA807A-9DB4-40A2-9B0A-F90D8F72A0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FD8F9E9-999D-4931-A9C5-6040B2D91FEF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{580B104C-87EA-4B4E-8DBB-FEEBBC5B377A}"/>
   </bookViews>
@@ -57,10 +57,10 @@
     <t>+525539181750</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>399</t>
+    <t>4</t>
+  </si>
+  <si>
+    <t>377</t>
   </si>
 </sst>
 </file>

--- a/data/Capacitacion/procesar/layoutPrueba.xlsx
+++ b/data/Capacitacion/procesar/layoutPrueba.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ikeasistencia0-my.sharepoint.com/personal/abolom_ikeasistencia_com/Documents/Documentos/1.-proyectos_ike/python/1.-Capacitacion_RH/2.-API.version_2.25022026/data/Capacitacion/procesar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="114_{21CA807A-9DB4-40A2-9B0A-F90D8F72A0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FD8F9E9-999D-4931-A9C5-6040B2D91FEF}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="114_{21CA807A-9DB4-40A2-9B0A-F90D8F72A0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34EED381-DA25-4A05-8D65-9D5B5F733B18}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{580B104C-87EA-4B4E-8DBB-FEEBBC5B377A}"/>
   </bookViews>
@@ -54,10 +54,10 @@
     <t>extension</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>+525539181750</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>377</t>
@@ -482,10 +482,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>11</v>
